--- a/data/nzd0587/nzd0587.xlsx
+++ b/data/nzd0587/nzd0587.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G469"/>
+  <dimension ref="A1:G471"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13089,6 +13089,60 @@
         <v>235.14</v>
       </c>
       <c r="G469" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="470">
+      <c r="A470" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-09 22:26:23+00:00</t>
+        </is>
+      </c>
+      <c r="B470" t="n">
+        <v>228.79</v>
+      </c>
+      <c r="C470" t="n">
+        <v>180.18</v>
+      </c>
+      <c r="D470" t="n">
+        <v>190.1</v>
+      </c>
+      <c r="E470" t="n">
+        <v>183.73</v>
+      </c>
+      <c r="F470" t="n">
+        <v>237.21</v>
+      </c>
+      <c r="G470" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="471">
+      <c r="A471" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-26 22:20:56+00:00</t>
+        </is>
+      </c>
+      <c r="B471" t="n">
+        <v>228.79</v>
+      </c>
+      <c r="C471" t="n">
+        <v>180.59</v>
+      </c>
+      <c r="D471" t="n">
+        <v>190.19</v>
+      </c>
+      <c r="E471" t="n">
+        <v>181.38</v>
+      </c>
+      <c r="F471" t="n">
+        <v>238.46</v>
+      </c>
+      <c r="G471" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -13105,7 +13159,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B541"/>
+  <dimension ref="A1:B544"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18518,6 +18572,36 @@
       </c>
       <c r="B541" t="n">
         <v>-0.92</v>
+      </c>
+    </row>
+    <row r="542">
+      <c r="A542" t="inlineStr">
+        <is>
+          <t>2026-07-09 22:30:00+00:00</t>
+        </is>
+      </c>
+      <c r="B542" t="n">
+        <v>0.74</v>
+      </c>
+    </row>
+    <row r="543">
+      <c r="A543" t="inlineStr">
+        <is>
+          <t>2026-07-10 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B543" t="n">
+        <v>0.92</v>
+      </c>
+    </row>
+    <row r="544">
+      <c r="A544" t="inlineStr">
+        <is>
+          <t>2026-07-26 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B544" t="n">
+        <v>0.41</v>
       </c>
     </row>
   </sheetData>
@@ -18680,28 +18764,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.0112885618117931</v>
+        <v>-0.005248660939947004</v>
       </c>
       <c r="J2" t="n">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="K2" t="n">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0002479224626029675</v>
+        <v>5.371778513629799e-05</v>
       </c>
       <c r="M2" t="n">
-        <v>3.621553926649974</v>
+        <v>3.635433074183835</v>
       </c>
       <c r="N2" t="n">
-        <v>31.48583080631345</v>
+        <v>31.58629570478884</v>
       </c>
       <c r="O2" t="n">
-        <v>5.611223646078763</v>
+        <v>5.620168654479048</v>
       </c>
       <c r="P2" t="n">
-        <v>221.6267518902112</v>
+        <v>221.5660358559442</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -18752,28 +18836,28 @@
         <v>0.1105</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.4525763093006209</v>
+        <v>-0.449993942840789</v>
       </c>
       <c r="J3" t="n">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="K3" t="n">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="L3" t="n">
-        <v>0.3046889185840906</v>
+        <v>0.3039709153931428</v>
       </c>
       <c r="M3" t="n">
-        <v>3.796537462627859</v>
+        <v>3.794099446065482</v>
       </c>
       <c r="N3" t="n">
-        <v>28.41156914486547</v>
+        <v>28.33302739900788</v>
       </c>
       <c r="O3" t="n">
-        <v>5.330250382943138</v>
+        <v>5.322877736620284</v>
       </c>
       <c r="P3" t="n">
-        <v>189.4276186024818</v>
+        <v>189.4015105178475</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -18824,28 +18908,28 @@
         <v>0.08160000000000001</v>
       </c>
       <c r="I4" t="n">
-        <v>0.06358258376492169</v>
+        <v>0.06689280002149123</v>
       </c>
       <c r="J4" t="n">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="K4" t="n">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="L4" t="n">
-        <v>0.004158789710139166</v>
+        <v>0.004639533533332796</v>
       </c>
       <c r="M4" t="n">
-        <v>6.225890007832641</v>
+        <v>6.212289640004798</v>
       </c>
       <c r="N4" t="n">
-        <v>58.84215550166099</v>
+        <v>58.66095232388238</v>
       </c>
       <c r="O4" t="n">
-        <v>7.670864064866551</v>
+        <v>7.65904382569276</v>
       </c>
       <c r="P4" t="n">
-        <v>184.357382878415</v>
+        <v>184.3239180912231</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -18896,28 +18980,28 @@
         <v>0.0892</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.1473941905186183</v>
+        <v>-0.1449029122862841</v>
       </c>
       <c r="J5" t="n">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="K5" t="n">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0107000019473823</v>
+        <v>0.01043952236793744</v>
       </c>
       <c r="M5" t="n">
-        <v>9.037682589802833</v>
+        <v>9.010693321419174</v>
       </c>
       <c r="N5" t="n">
-        <v>122.093903709197</v>
+        <v>121.6186644529232</v>
       </c>
       <c r="O5" t="n">
-        <v>11.0496110207191</v>
+        <v>11.02808525778266</v>
       </c>
       <c r="P5" t="n">
-        <v>183.4694072098731</v>
+        <v>183.4442318083235</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -18968,28 +19052,28 @@
         <v>0.2</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.130365756104742</v>
+        <v>-0.1304946720050987</v>
       </c>
       <c r="J6" t="n">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="K6" t="n">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="L6" t="n">
-        <v>0.02932227731408033</v>
+        <v>0.02965085638495346</v>
       </c>
       <c r="M6" t="n">
-        <v>4.584932032435193</v>
+        <v>4.568124760107986</v>
       </c>
       <c r="N6" t="n">
-        <v>34.19743376046522</v>
+        <v>34.05341219019238</v>
       </c>
       <c r="O6" t="n">
-        <v>5.847857193918574</v>
+        <v>5.835530155023824</v>
       </c>
       <c r="P6" t="n">
-        <v>241.5160947405063</v>
+        <v>241.5173926244649</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -19027,7 +19111,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G469"/>
+  <dimension ref="A1:G471"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -36363,6 +36447,80 @@
         </is>
       </c>
     </row>
+    <row r="470">
+      <c r="A470" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-09 22:26:23+00:00</t>
+        </is>
+      </c>
+      <c r="B470" t="inlineStr">
+        <is>
+          <t>-46.889785731308024,168.13907332518437</t>
+        </is>
+      </c>
+      <c r="C470" t="inlineStr">
+        <is>
+          <t>-46.88895685972958,168.13886600164304</t>
+        </is>
+      </c>
+      <c r="D470" t="inlineStr">
+        <is>
+          <t>-46.88887605750562,168.13776688909658</t>
+        </is>
+      </c>
+      <c r="E470" t="inlineStr">
+        <is>
+          <t>-46.889038785488545,168.13674240915455</t>
+        </is>
+      </c>
+      <c r="F470" t="inlineStr">
+        <is>
+          <t>-46.8897139959124,168.13595515393578</t>
+        </is>
+      </c>
+      <c r="G470" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="471">
+      <c r="A471" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-26 22:20:56+00:00</t>
+        </is>
+      </c>
+      <c r="B471" t="inlineStr">
+        <is>
+          <t>-46.889785731308024,168.13907332518437</t>
+        </is>
+      </c>
+      <c r="C471" t="inlineStr">
+        <is>
+          <t>-46.88895927687184,168.13886194761702</t>
+        </is>
+      </c>
+      <c r="D471" t="inlineStr">
+        <is>
+          <t>-46.88887682830979,168.13776724519303</t>
+        </is>
+      </c>
+      <c r="E471" t="inlineStr">
+        <is>
+          <t>-46.889018658864934,168.1367331114515</t>
+        </is>
+      </c>
+      <c r="F471" t="inlineStr">
+        <is>
+          <t>-46.88972469835831,168.13596011429036</t>
+        </is>
+      </c>
+      <c r="G471" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0587/nzd0587.xlsx
+++ b/data/nzd0587/nzd0587.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G471"/>
+  <dimension ref="A1:G474"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13145,6 +13145,87 @@
       <c r="G471" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="472">
+      <c r="A472" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-02 22:27:10+00:00</t>
+        </is>
+      </c>
+      <c r="B472" t="n">
+        <v>227.84</v>
+      </c>
+      <c r="C472" t="n">
+        <v>180.59</v>
+      </c>
+      <c r="D472" t="n">
+        <v>189.85</v>
+      </c>
+      <c r="E472" t="n">
+        <v>182.22</v>
+      </c>
+      <c r="F472" t="n">
+        <v>239.26</v>
+      </c>
+      <c r="G472" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="473">
+      <c r="A473" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-10 22:26:38+00:00</t>
+        </is>
+      </c>
+      <c r="B473" t="n">
+        <v>226.38</v>
+      </c>
+      <c r="C473" t="n">
+        <v>181.38</v>
+      </c>
+      <c r="D473" t="n">
+        <v>189.53</v>
+      </c>
+      <c r="E473" t="n">
+        <v>179.06</v>
+      </c>
+      <c r="F473" t="n">
+        <v>239.65</v>
+      </c>
+      <c r="G473" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="474">
+      <c r="A474" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-19 22:20:56+00:00</t>
+        </is>
+      </c>
+      <c r="B474" t="n">
+        <v>222.63</v>
+      </c>
+      <c r="C474" t="n">
+        <v>180.55</v>
+      </c>
+      <c r="D474" t="n">
+        <v>189.42</v>
+      </c>
+      <c r="E474" t="n">
+        <v>179.18</v>
+      </c>
+      <c r="F474" t="n">
+        <v>240.36</v>
+      </c>
+      <c r="G474" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -13159,7 +13240,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B544"/>
+  <dimension ref="A1:B547"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18602,6 +18683,36 @@
       </c>
       <c r="B544" t="n">
         <v>0.41</v>
+      </c>
+    </row>
+    <row r="545">
+      <c r="A545" t="inlineStr">
+        <is>
+          <t>2026-08-02 22:30:00+00:00</t>
+        </is>
+      </c>
+      <c r="B545" t="n">
+        <v>-0.75</v>
+      </c>
+    </row>
+    <row r="546">
+      <c r="A546" t="inlineStr">
+        <is>
+          <t>2026-08-10 22:30:00+00:00</t>
+        </is>
+      </c>
+      <c r="B546" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+    </row>
+    <row r="547">
+      <c r="A547" t="inlineStr">
+        <is>
+          <t>2026-08-19 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B547" t="n">
+        <v>0.11</v>
       </c>
     </row>
   </sheetData>
@@ -18764,28 +18875,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.005248660939947004</v>
+        <v>-0.0002456194551210819</v>
       </c>
       <c r="J2" t="n">
-        <v>470</v>
+        <v>473</v>
       </c>
       <c r="K2" t="n">
-        <v>469</v>
+        <v>472</v>
       </c>
       <c r="L2" t="n">
-        <v>5.371778513629799e-05</v>
+        <v>1.187882682218699e-07</v>
       </c>
       <c r="M2" t="n">
-        <v>3.635433074183835</v>
+        <v>3.637085958545692</v>
       </c>
       <c r="N2" t="n">
-        <v>31.58629570478884</v>
+        <v>31.52551700463373</v>
       </c>
       <c r="O2" t="n">
-        <v>5.620168654479048</v>
+        <v>5.614758855430368</v>
       </c>
       <c r="P2" t="n">
-        <v>221.5660358559442</v>
+        <v>221.5156184084287</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -18836,28 +18947,28 @@
         <v>0.1105</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.449993942840789</v>
+        <v>-0.44564918284175</v>
       </c>
       <c r="J3" t="n">
-        <v>470</v>
+        <v>473</v>
       </c>
       <c r="K3" t="n">
-        <v>469</v>
+        <v>472</v>
       </c>
       <c r="L3" t="n">
-        <v>0.3039709153931428</v>
+        <v>0.3022495071672096</v>
       </c>
       <c r="M3" t="n">
-        <v>3.794099446065482</v>
+        <v>3.793266537210583</v>
       </c>
       <c r="N3" t="n">
-        <v>28.33302739900788</v>
+        <v>28.23529694051758</v>
       </c>
       <c r="O3" t="n">
-        <v>5.322877736620284</v>
+        <v>5.313689578863031</v>
       </c>
       <c r="P3" t="n">
-        <v>189.4015105178475</v>
+        <v>189.3574607828402</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -18908,28 +19019,28 @@
         <v>0.08160000000000001</v>
       </c>
       <c r="I4" t="n">
-        <v>0.06689280002149123</v>
+        <v>0.0710530681409403</v>
       </c>
       <c r="J4" t="n">
-        <v>470</v>
+        <v>473</v>
       </c>
       <c r="K4" t="n">
-        <v>469</v>
+        <v>472</v>
       </c>
       <c r="L4" t="n">
-        <v>0.004639533533332796</v>
+        <v>0.005298979825547057</v>
       </c>
       <c r="M4" t="n">
-        <v>6.212289640004798</v>
+        <v>6.18914917725982</v>
       </c>
       <c r="N4" t="n">
-        <v>58.66095232388238</v>
+        <v>58.36299212884349</v>
       </c>
       <c r="O4" t="n">
-        <v>7.65904382569276</v>
+        <v>7.639567535459287</v>
       </c>
       <c r="P4" t="n">
-        <v>184.3239180912231</v>
+        <v>184.2817404420586</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -18980,28 +19091,28 @@
         <v>0.0892</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.1449029122862841</v>
+        <v>-0.1441431857443813</v>
       </c>
       <c r="J5" t="n">
-        <v>470</v>
+        <v>473</v>
       </c>
       <c r="K5" t="n">
-        <v>469</v>
+        <v>472</v>
       </c>
       <c r="L5" t="n">
-        <v>0.01043952236793744</v>
+        <v>0.01047604454106998</v>
       </c>
       <c r="M5" t="n">
-        <v>9.010693321419174</v>
+        <v>8.960390763688912</v>
       </c>
       <c r="N5" t="n">
-        <v>121.6186644529232</v>
+        <v>120.8617250765544</v>
       </c>
       <c r="O5" t="n">
-        <v>11.02808525778266</v>
+        <v>10.99371297954219</v>
       </c>
       <c r="P5" t="n">
-        <v>183.4442318083235</v>
+        <v>183.4365417906291</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -19052,28 +19163,28 @@
         <v>0.2</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.1304946720050987</v>
+        <v>-0.1283677112496798</v>
       </c>
       <c r="J6" t="n">
-        <v>470</v>
+        <v>473</v>
       </c>
       <c r="K6" t="n">
-        <v>469</v>
+        <v>472</v>
       </c>
       <c r="L6" t="n">
-        <v>0.02965085638495346</v>
+        <v>0.02910038168622808</v>
       </c>
       <c r="M6" t="n">
-        <v>4.568124760107986</v>
+        <v>4.549284568024711</v>
       </c>
       <c r="N6" t="n">
-        <v>34.05341219019238</v>
+        <v>33.85780666989097</v>
       </c>
       <c r="O6" t="n">
-        <v>5.835530155023824</v>
+        <v>5.81874614241685</v>
       </c>
       <c r="P6" t="n">
-        <v>241.5173926244649</v>
+        <v>241.4958234155275</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -19111,7 +19222,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G471"/>
+  <dimension ref="A1:G474"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -36521,6 +36632,117 @@
         </is>
       </c>
     </row>
+    <row r="472">
+      <c r="A472" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-02 22:27:10+00:00</t>
+        </is>
+      </c>
+      <c r="B472" t="inlineStr">
+        <is>
+          <t>-46.889780130599995,168.13908271878964</t>
+        </is>
+      </c>
+      <c r="C472" t="inlineStr">
+        <is>
+          <t>-46.88895927687184,168.13886194761702</t>
+        </is>
+      </c>
+      <c r="D472" t="inlineStr">
+        <is>
+          <t>-46.88887391638291,168.1377658999398</t>
+        </is>
+      </c>
+      <c r="E472" t="inlineStr">
+        <is>
+          <t>-46.88902585306237,168.13673643488502</t>
+        </is>
+      </c>
+      <c r="F472" t="inlineStr">
+        <is>
+          <t>-46.889731547923596,168.13596328891825</t>
+        </is>
+      </c>
+      <c r="G472" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="473">
+      <c r="A473" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-10 22:26:38+00:00</t>
+        </is>
+      </c>
+      <c r="B473" t="inlineStr">
+        <is>
+          <t>-46.88977152319442,168.139097155274</t>
+        </is>
+      </c>
+      <c r="C473" t="inlineStr">
+        <is>
+          <t>-46.88896393429182,168.13885413619997</t>
+        </is>
+      </c>
+      <c r="D473" t="inlineStr">
+        <is>
+          <t>-46.88887117574582,168.13776463381924</t>
+        </is>
+      </c>
+      <c r="E473" t="inlineStr">
+        <is>
+          <t>-46.88899878917639,168.13672393244877</t>
+        </is>
+      </c>
+      <c r="F473" t="inlineStr">
+        <is>
+          <t>-46.889734887086654,168.13596483654965</t>
+        </is>
+      </c>
+      <c r="G473" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="474">
+      <c r="A474" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-19 22:20:56+00:00</t>
+        </is>
+      </c>
+      <c r="B474" t="inlineStr">
+        <is>
+          <t>-46.889749415122964,168.13913423526404</t>
+        </is>
+      </c>
+      <c r="C474" t="inlineStr">
+        <is>
+          <t>-46.888959041053084,168.13886234313176</t>
+        </is>
+      </c>
+      <c r="D474" t="inlineStr">
+        <is>
+          <t>-46.88887023365183,168.1377641985903</t>
+        </is>
+      </c>
+      <c r="E474" t="inlineStr">
+        <is>
+          <t>-46.88899981691892,168.13672440722462</t>
+        </is>
+      </c>
+      <c r="F474" t="inlineStr">
+        <is>
+          <t>-46.88974096607578,168.13596765403284</t>
+        </is>
+      </c>
+      <c r="G474" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0587/nzd0587.xlsx
+++ b/data/nzd0587/nzd0587.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G474"/>
+  <dimension ref="A1:G476"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13226,6 +13226,60 @@
       <c r="G474" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="475">
+      <c r="A475" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-11 22:26:48+00:00</t>
+        </is>
+      </c>
+      <c r="B475" t="n">
+        <v>220.94</v>
+      </c>
+      <c r="C475" t="n">
+        <v>180.9</v>
+      </c>
+      <c r="D475" t="n">
+        <v>189.31</v>
+      </c>
+      <c r="E475" t="n">
+        <v>177.61</v>
+      </c>
+      <c r="F475" t="n">
+        <v>240.85</v>
+      </c>
+      <c r="G475" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="476">
+      <c r="A476" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-28 22:21:16+00:00</t>
+        </is>
+      </c>
+      <c r="B476" t="n">
+        <v>216.99</v>
+      </c>
+      <c r="C476" t="n">
+        <v>179.94</v>
+      </c>
+      <c r="D476" t="n">
+        <v>190.21</v>
+      </c>
+      <c r="E476" t="n">
+        <v>178.74</v>
+      </c>
+      <c r="F476" t="n">
+        <v>241.49</v>
+      </c>
+      <c r="G476" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -13240,7 +13294,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B547"/>
+  <dimension ref="A1:B549"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18713,6 +18767,26 @@
       </c>
       <c r="B547" t="n">
         <v>0.11</v>
+      </c>
+    </row>
+    <row r="548">
+      <c r="A548" t="inlineStr">
+        <is>
+          <t>2026-09-11 22:30:00+00:00</t>
+        </is>
+      </c>
+      <c r="B548" t="n">
+        <v>-0.37</v>
+      </c>
+    </row>
+    <row r="549">
+      <c r="A549" t="inlineStr">
+        <is>
+          <t>2026-09-28 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B549" t="n">
+        <v>-0.77</v>
       </c>
     </row>
   </sheetData>
@@ -18875,28 +18949,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.0002456194551210819</v>
+        <v>-0.002266439602989052</v>
       </c>
       <c r="J2" t="n">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="K2" t="n">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="L2" t="n">
-        <v>1.187882682218699e-07</v>
+        <v>1.019547031599899e-05</v>
       </c>
       <c r="M2" t="n">
-        <v>3.637085958545692</v>
+        <v>3.632957203876034</v>
       </c>
       <c r="N2" t="n">
-        <v>31.52551700463373</v>
+        <v>31.4359641802953</v>
       </c>
       <c r="O2" t="n">
-        <v>5.614758855430368</v>
+        <v>5.606778413696701</v>
       </c>
       <c r="P2" t="n">
-        <v>221.5156184084287</v>
+        <v>221.5361088494446</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -18947,28 +19021,28 @@
         <v>0.1105</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.44564918284175</v>
+        <v>-0.4431174091145426</v>
       </c>
       <c r="J3" t="n">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="K3" t="n">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="L3" t="n">
-        <v>0.3022495071672096</v>
+        <v>0.3015112305389683</v>
       </c>
       <c r="M3" t="n">
-        <v>3.793266537210583</v>
+        <v>3.791061454409251</v>
       </c>
       <c r="N3" t="n">
-        <v>28.23529694051758</v>
+        <v>28.15907511528395</v>
       </c>
       <c r="O3" t="n">
-        <v>5.313689578863031</v>
+        <v>5.30651251909236</v>
       </c>
       <c r="P3" t="n">
-        <v>189.3574607828402</v>
+        <v>189.3316706812491</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -19019,28 +19093,28 @@
         <v>0.08160000000000001</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0710530681409403</v>
+        <v>0.07388188504120753</v>
       </c>
       <c r="J4" t="n">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="K4" t="n">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="L4" t="n">
-        <v>0.005298979825547057</v>
+        <v>0.005775461691474693</v>
       </c>
       <c r="M4" t="n">
-        <v>6.18914917725982</v>
+        <v>6.174084480045913</v>
       </c>
       <c r="N4" t="n">
-        <v>58.36299212884349</v>
+        <v>58.16992868648013</v>
       </c>
       <c r="O4" t="n">
-        <v>7.639567535459287</v>
+        <v>7.626921311150399</v>
       </c>
       <c r="P4" t="n">
-        <v>184.2817404420586</v>
+        <v>184.2529162508956</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -19091,28 +19165,28 @@
         <v>0.0892</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.1441431857443813</v>
+        <v>-0.1452169970659743</v>
       </c>
       <c r="J5" t="n">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="K5" t="n">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="L5" t="n">
-        <v>0.01047604454106998</v>
+        <v>0.0107297609539927</v>
       </c>
       <c r="M5" t="n">
-        <v>8.960390763688912</v>
+        <v>8.928791514606974</v>
       </c>
       <c r="N5" t="n">
-        <v>120.8617250765544</v>
+        <v>120.3606784390292</v>
       </c>
       <c r="O5" t="n">
-        <v>10.99371297954219</v>
+        <v>10.97090144149646</v>
       </c>
       <c r="P5" t="n">
-        <v>183.4365417906291</v>
+        <v>183.4474771714282</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -19163,28 +19237,28 @@
         <v>0.2</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.1283677112496798</v>
+        <v>-0.1258459666092576</v>
       </c>
       <c r="J6" t="n">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="K6" t="n">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="L6" t="n">
-        <v>0.02910038168622808</v>
+        <v>0.0282232073004689</v>
       </c>
       <c r="M6" t="n">
-        <v>4.549284568024711</v>
+        <v>4.542006097315774</v>
       </c>
       <c r="N6" t="n">
-        <v>33.85780666989097</v>
+        <v>33.75697992075193</v>
       </c>
       <c r="O6" t="n">
-        <v>5.81874614241685</v>
+        <v>5.810075724183974</v>
       </c>
       <c r="P6" t="n">
-        <v>241.4958234155275</v>
+        <v>241.4701287989029</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -19222,7 +19296,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G474"/>
+  <dimension ref="A1:G476"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -36743,6 +36817,80 @@
         </is>
       </c>
     </row>
+    <row r="475">
+      <c r="A475" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-11 22:26:48+00:00</t>
+        </is>
+      </c>
+      <c r="B475" t="inlineStr">
+        <is>
+          <t>-46.88973945174775,168.13915094596965</t>
+        </is>
+      </c>
+      <c r="C475" t="inlineStr">
+        <is>
+          <t>-46.888961104467086,168.13885888237758</t>
+        </is>
+      </c>
+      <c r="D475" t="inlineStr">
+        <is>
+          <t>-46.888869291557825,168.1377637633614</t>
+        </is>
+      </c>
+      <c r="E475" t="inlineStr">
+        <is>
+          <t>-46.8889863706208,168.13671819557527</t>
+        </is>
+      </c>
+      <c r="F475" t="inlineStr">
+        <is>
+          <t>-46.88974516143444,168.13596959849343</t>
+        </is>
+      </c>
+      <c r="G475" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="476">
+      <c r="A476" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-28 22:21:16+00:00</t>
+        </is>
+      </c>
+      <c r="B476" t="inlineStr">
+        <is>
+          <t>-46.88971616455855,168.13919000351197</t>
+        </is>
+      </c>
+      <c r="C476" t="inlineStr">
+        <is>
+          <t>-46.88895544481697,168.1388683747313</t>
+        </is>
+      </c>
+      <c r="D476" t="inlineStr">
+        <is>
+          <t>-46.888876999599624,168.13776732432558</t>
+        </is>
+      </c>
+      <c r="E476" t="inlineStr">
+        <is>
+          <t>-46.88899604852967,168.13672266637994</t>
+        </is>
+      </c>
+      <c r="F476" t="inlineStr">
+        <is>
+          <t>-46.889750641086536,168.13597213819747</t>
+        </is>
+      </c>
+      <c r="G476" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
